--- a/Tracker Update.xlsx
+++ b/Tracker Update.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
   <si>
     <t>DATE</t>
   </si>
@@ -796,6 +796,27 @@
     <t xml:space="preserve">Context - context.id, context.type (ex. before,after...), context.method,context.app,context.service,context.context.result,context.error,context.params (headers,host related),context.data(incomind data related - ex.body in express),statusCode (manualy we need to set 201,200,404) like this ,
 Types -before, after,around,error
 Methods - find,get,patch,update,remove</t>
+  </si>
+  <si>
+    <t>20/2/2026</t>
+  </si>
+  <si>
+    <t>SDLC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Models and Testing Types</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waterfall Model, Iterative Model, Spiral model, V- Modal, Big Ban Model, Agile Model
+Testing Types - Manual Testing, Automation Testing , White Box , Black Box, Functionali , Non FUnctional, Performance
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manual Testing - Whitebox, Black Box
+Black Box - Functional, Non Functionalx
+Functional - Unit Testing, Integration testing, System Testing
+Non functional - Performance,Usability, Compatibility
+Performance - Load Testing, Stress Testing, Scalibility Testing, Stability Testing</t>
   </si>
 </sst>
 </file>
@@ -927,7 +948,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -968,9 +989,6 @@
     <xf fontId="8" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -999,6 +1017,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="3" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="3" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1813,7 +1837,7 @@
       <c r="D15" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="8" t="s">
         <v>47</v>
       </c>
       <c r="F15" s="8"/>
@@ -1851,205 +1875,287 @@
       <c r="F17" s="8"/>
     </row>
     <row r="18" ht="114">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="15"/>
+      <c r="F18" s="14"/>
     </row>
     <row r="19" ht="57">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15" t="s">
+      <c r="C19" s="14"/>
+      <c r="D19" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="E19" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="F19" s="15"/>
+      <c r="F19" s="14"/>
     </row>
     <row r="20" ht="99.75">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15" t="s">
+      <c r="C20" s="14"/>
+      <c r="D20" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="F20" s="15"/>
+      <c r="F20" s="14"/>
     </row>
     <row r="21" ht="213.75">
-      <c r="A21" s="16">
+      <c r="A21" s="15">
         <v>46055</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D21" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="F21" s="15"/>
+      <c r="F21" s="14"/>
     </row>
     <row r="22" ht="156.75">
-      <c r="A22" s="17">
+      <c r="A22" s="16">
         <v>46083</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="E22" s="15" t="s">
+      <c r="E22" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="F22" s="15"/>
+      <c r="F22" s="14"/>
     </row>
     <row r="23" ht="213.75">
-      <c r="A23" s="17">
+      <c r="A23" s="16">
         <v>46114</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="E23" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="F23" s="15"/>
+      <c r="F23" s="14"/>
       <c r="I23" s="1"/>
     </row>
     <row r="24" ht="199.5">
-      <c r="A24" s="17">
+      <c r="A24" s="16">
         <v>46175</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E24" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="F24" s="15"/>
+      <c r="F24" s="14"/>
     </row>
     <row r="25" ht="85.5">
-      <c r="A25" s="17">
+      <c r="A25" s="16">
         <v>46297</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="E25" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="F25" s="15"/>
+      <c r="F25" s="14"/>
     </row>
     <row r="26" ht="213.75">
-      <c r="A26" s="18">
+      <c r="A26" s="17">
         <v>46328</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="D26" s="19" t="s">
+      <c r="D26" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="E26" s="19" t="s">
+      <c r="E26" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="F26" s="19"/>
+      <c r="F26" s="18"/>
     </row>
     <row r="27" ht="57">
-      <c r="A27" s="20">
+      <c r="A27" s="19">
         <v>46358</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="B27" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="C27" s="21" t="s">
+      <c r="C27" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="D27" s="21" t="s">
+      <c r="D27" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="E27" s="22"/>
-      <c r="F27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="20"/>
     </row>
     <row r="28" ht="114">
-      <c r="A28" s="23" t="s">
+      <c r="A28" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="B28" s="23" t="s">
+      <c r="B28" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="C28" s="23" t="s">
+      <c r="C28" s="22" t="s">
         <v>95</v>
       </c>
       <c r="D28" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="E28" s="23" t="s">
+      <c r="E28" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="F28" s="24"/>
-    </row>
-    <row r="29" ht="14.25">
-      <c r="A29" s="19"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
+      <c r="F28" s="22"/>
+    </row>
+    <row r="29" ht="99.75">
+      <c r="A29" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="B29" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="E29" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="F29" s="18"/>
+    </row>
+    <row r="30" ht="54.75" customHeight="1">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+    </row>
+    <row r="31" ht="14.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+    </row>
+    <row r="32" ht="14.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+    </row>
+    <row r="33" ht="14.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+    </row>
+    <row r="34" ht="14.25">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+    </row>
+    <row r="35" ht="14.25">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+    </row>
+    <row r="36" ht="14.25">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+    </row>
+    <row r="37" ht="14.25">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+    </row>
+    <row r="38" ht="14.25">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="1"/>
